--- a/data/trans_orig/P36BPD07_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_R-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>583319</t>
+          <t>583341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>616338</t>
+          <t>616207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>582703</t>
+          <t>584273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>615194</t>
+          <t>614839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1175391</t>
+          <t>1176219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1223269</t>
+          <t>1222491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55067</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88086</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85640</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>117257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164357</t>
+          <t>163529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>816703</t>
+          <t>817574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>867486</t>
+          <t>867205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>880735</t>
+          <t>880519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>923694</t>
+          <t>924610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1715199</t>
+          <t>1715853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1782595</t>
+          <t>1778401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151463</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202246</t>
+          <t>201375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>118303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162178</t>
+          <t>162394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>279267</t>
+          <t>283461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346663</t>
+          <t>346009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>599461</t>
+          <t>599825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>644694</t>
+          <t>643930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>619639</t>
+          <t>620882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>662761</t>
+          <t>664568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1232140</t>
+          <t>1237738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1294993</t>
+          <t>1297499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156612</t>
+          <t>156248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114577</t>
+          <t>112770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157699</t>
+          <t>156456</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238418</t>
+          <t>235912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301271</t>
+          <t>295673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>752902</t>
+          <t>751034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>797201</t>
+          <t>795796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>885235</t>
+          <t>884746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>928737</t>
+          <t>926495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1651357</t>
+          <t>1649530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1713757</t>
+          <t>1715303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127478</t>
+          <t>128883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171777</t>
+          <t>173645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104937</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148439</t>
+          <t>148928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>244595</t>
+          <t>243049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306995</t>
+          <t>308822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2800989</t>
+          <t>2803345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2889160</t>
+          <t>2886551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3014471</t>
+          <t>3014342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3093012</t>
+          <t>3093238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5843895</t>
+          <t>5838447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5960210</t>
+          <t>5961622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>472553</t>
+          <t>516047</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>445774</t>
+          <t>490833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>495513</t>
+          <t>539863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>544348</t>
+          <t>586541</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>525440</t>
+          <t>564505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>560538</t>
+          <t>604964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1016900</t>
+          <t>1102588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>988068</t>
+          <t>1069538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1045716</t>
+          <t>1131038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160940</t>
+          <t>172508</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>148692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187719</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>130450</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114260</t>
+          <t>127091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149358</t>
+          <t>167550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>291391</t>
+          <t>318022</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>289572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320223</t>
+          <t>351072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633493</t>
+          <t>688555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674798</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308291</t>
+          <t>1420610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>882197</t>
+          <t>704343</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>788390</t>
+          <t>668371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1047127</t>
+          <t>742387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>696886</t>
+          <t>770271</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>671552</t>
+          <t>742960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>720214</t>
+          <t>796466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1579082</t>
+          <t>1474615</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1492754</t>
+          <t>1431050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1760550</t>
+          <t>1519346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>309830</t>
+          <t>343709</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144900</t>
+          <t>305665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403637</t>
+          <t>379681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>260897</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237569</t>
+          <t>272881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>286231</t>
+          <t>326387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>570728</t>
+          <t>642785</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389260</t>
+          <t>598054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>657056</t>
+          <t>686350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957783</t>
+          <t>1069347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149810</t>
+          <t>2117400</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,27 +3359,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>534829</t>
+          <t>609852</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>508016</t>
+          <t>577592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>560181</t>
+          <t>638371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>786721</t>
+          <t>639227</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>735388</t>
+          <t>617252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>860902</t>
+          <t>660922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1321550</t>
+          <t>1249079</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1264256</t>
+          <t>1212799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1426882</t>
+          <t>1284366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -3472,22 +3472,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>169851</t>
+          <t>193221</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144499</t>
+          <t>164702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196664</t>
+          <t>225481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146645</t>
+          <t>173032</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72464</t>
+          <t>151337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197978</t>
+          <t>195007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>316496</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211164</t>
+          <t>330966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>373790</t>
+          <t>402533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>662598</t>
+          <t>690762</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>631700</t>
+          <t>658466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>694905</t>
+          <t>721830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>858346</t>
+          <t>848381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>828277</t>
+          <t>819475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>901696</t>
+          <t>873137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1520945</t>
+          <t>1539142</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1476416</t>
+          <t>1497931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1578119</t>
+          <t>1583955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262177</t>
+          <t>297165</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229870</t>
+          <t>266097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293075</t>
+          <t>329461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>232002</t>
+          <t>265936</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188652</t>
+          <t>241180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262071</t>
+          <t>294842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>494179</t>
+          <t>563101</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437005</t>
+          <t>518288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538708</t>
+          <t>604312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924775</t>
+          <t>987927</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090348</t>
+          <t>1114317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2015124</t>
+          <t>2102243</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
